--- a/docs/mmm.xlsx
+++ b/docs/mmm.xlsx
@@ -23,6 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="&amp;quot;¥&amp;quot;#,##0.00"/>
+  </numFmts>
   <fonts count="10">
     <font>
       <sz val="12"/>
@@ -120,8 +123,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -319,20 +330,20 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
     </row>

--- a/docs/mmm.xlsx
+++ b/docs/mmm.xlsx
@@ -52,6 +52,7 @@
     </font>
     <font>
       <b/>
+      <strike/>
       <sz val="12"/>
       <color rgb="1"/>
       <name val="等线"/>
@@ -69,7 +70,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <strike/>
+      <u val="single"/>
       <sz val="12"/>
       <color rgb="1"/>
       <name val="等线"/>
@@ -349,10 +350,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>999.804000</v>
+        <v>999.804</v>
       </c>
       <c r="B5">
-        <v>443888.567890</v>
+        <v>443888.56789</v>
       </c>
     </row>
   </sheetData>
